--- a/results/job_matches_2026-10-12.xlsx
+++ b/results/job_matches_2026-10-12.xlsx
@@ -456,60 +456,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Hub-Remote: DC or Philly Metro)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alexandria, VA, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2162b37870f256</t>
+          <t>https://www.indeed.com/viewjob?jk=6cdaf76f16c112ab</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps Engineer (Hub-Remote: DC or Philly Metro)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Alexandria, VA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, BigQuery, Spark</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a4ee98072606c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cf2162b37870f256</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, PySpark, DynamoDB</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,67 +554,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4383f4a43e40098</t>
+          <t>https://www.indeed.com/viewjob?jk=89a4ee98072606c4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>Well Beam Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pasadena, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0abbf70775a0e95</t>
+          <t>https://www.indeed.com/viewjob?jk=2488604858d657c6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Paytm One97 Communications</t>
+          <t>Innovya Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Storden, MN, USA USA</t>
+          <t>Pasadena, CA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de54c7ef6aacffc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0abbf70775a0e95</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-12.xlsx
+++ b/results/job_matches_2026-10-12.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,52 +526,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>American IT Resource Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Schaumburg, IL, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, BigQuery, Spark</t>
+          <t>AWS, S3, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a4ee98072606c4</t>
+          <t>https://www.indeed.com/viewjob?jk=986d945ea6a31b4a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Data Product Owner</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Well Beam Inc</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Milpitas, CA, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,42 +589,357 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488604858d657c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8f393df2dff71eea</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Innovya Technologies</t>
+          <t>Well Beam Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pasadena, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2488604858d657c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kiewit Corporation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Omaha, NE, USA USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Cloud Storage, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f3210094a7b1a68</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer (Python / Cloud / React)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Hartford, CT, USA USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8949c2d4ce773826</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Google Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vibhutechinc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Sqoop, MapReduce, HBase, Oozie</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65a614c7d6ae8592</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Advisor_BCDA1J</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ENGIE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Houston, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66bdadf1084f2459</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Madison, WI, USA USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>11.8</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0abbf70775a0e95</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8dc3509acac22dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Microsoft Fabric Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Irving, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbb1a7f642a73abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, USA USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da31ce66bd2bac28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tampa, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46b2f59b4f79c5de</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Siemens Healthineers</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Malvern, PA, USA USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97b19b6f1b88b438</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-12.xlsx
+++ b/results/job_matches_2026-10-12.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Databricks Platform Engineer (Remote US)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,67 +484,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cdaf76f16c112ab</t>
+          <t>https://www.indeed.com/viewjob?jk=567f4ddfd333af1a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Hub-Remote: DC or Philly Metro)</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>CALLISTOFUSION</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alexandria, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2162b37870f256</t>
+          <t>https://www.indeed.com/viewjob?jk=2ef0def19f3a7249</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>C2 - Data Architect/Data Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American IT Resource Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986d945ea6a31b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff331119fd9599f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Product Owner</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Milpitas, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f393df2dff71eea</t>
+          <t>https://www.indeed.com/viewjob?jk=df9e8fec032270fc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Azure Ops/AI Engineer (US Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Well Beam Inc</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488604858d657c6</t>
+          <t>https://www.indeed.com/viewjob?jk=194ae6ae0e83b1f9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Applications Development Programmer Analyst I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>University of Arizona</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Omaha, NE, USA USA</t>
+          <t>Tucson, AZ, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Cloud Storage, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3210094a7b1a68</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3dedad49f70365</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Python / Cloud / React)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8949c2d4ce773826</t>
+          <t>https://www.indeed.com/viewjob?jk=6cdaf76f16c112ab</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Google Cloud Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vibhutechinc</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Sqoop, MapReduce, HBase, Oozie</t>
+          <t>AWS, ECS, Azure, GCP, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a614c7d6ae8592</t>
+          <t>https://www.indeed.com/viewjob?jk=f97384085c269653</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Advisor_BCDA1J</t>
+          <t>Senior Data Product Owner</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENGIE</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Milpitas, CA, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66bdadf1084f2459</t>
+          <t>https://www.indeed.com/viewjob?jk=8f393df2dff71eea</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Madison, WI, USA USA</t>
+          <t>O'Fallon, MO, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8dc3509acac22dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6e2a8d9e54239f64</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Well Beam Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb1a7f642a73abe</t>
+          <t>https://www.indeed.com/viewjob?jk=2488604858d657c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Mid Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Trinzic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, USA USA</t>
+          <t>Colorado Springs, CO, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da31ce66bd2bac28</t>
+          <t>https://www.indeed.com/viewjob?jk=cd94caafa09b4992</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Snowflake, Informatica PowerCenter, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,42 +904,1197 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b2f59b4f79c5de</t>
+          <t>https://www.indeed.com/viewjob?jk=b0deb4be66811f62</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Jr Software Developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Trinzic</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, USA USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0799847319eb195f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kiewit Corporation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Omaha, NE, USA USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Cloud Storage, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f3210094a7b1a68</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Cloud Platform Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Round Rock, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c11d54c5ad58b814</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Cloud Ops Engineer I – SRE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CaseWorthy</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e393b702b8050654</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>O'Fallon, MO, USA USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9c3d1ebb5b991ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6dfe72a31f423d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Azure Cloud Data Engineer(Korean Bilingual)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sbt Global</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Irvine, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab8d843a20197d70</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cox Automotive</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Carmel, IN, USA USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a11f8decdf7c70c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Platform &amp; Orchestration</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arvest Bank</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20f399d6b24294ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Analyst</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Par Pacific Holdings</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Houston, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a52dd27f1d6db31a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Development Engineer II - ArcGIS Enterprise</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Esri</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Redlands, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2484818a2b3b3775</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Developer, Full Stack</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Northramp</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Washington, DC, USA USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99ba8e362522f5e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IT Software Developer, Senior</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Diego, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1dc1d6539719ae41</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Advisor_BCDA1J</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ENGIE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Houston, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66bdadf1084f2459</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Report Developer II</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>University Hospitals</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Shaker Heights, OH, USA USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>EMR, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, Dimension Tables, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1da220a93db0e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vforce Infotech</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Edison, NJ, USA USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77b874109ab17ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Microsoft Fabric Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Irving, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbb1a7f642a73abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, USA USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da31ce66bd2bac28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Analyst, Business Intelligence &amp; Data Engineering</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Washington, DC, USA USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, ETL, dbt, Tableau, Airflow</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f559355e662e5e19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Developer Engineer in Testing</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EBS-MINDS IT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>S3, RDS, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=003e39d009345e9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Snowflake dbt Developer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Victaulic</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VA, USA USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef7cf14a046fe980</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67fbdcf58161d238</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Databricks Data Analyst</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Stitch Consulting Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>USA USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Unity Catalog, BigQuery, Spark, PySpark, Snowflake, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=287dcd1bbf750e92</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bitful Consulting</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wadsworth, OH, USA USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Oracle, Data Modeling, ETL, ELT, Tableau</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63e623558d354d72</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Knowledge Graph / Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OtterSoft</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3de2e9539589d93</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bitful Consulting</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tampa, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Oracle, Data Modeling, ETL, ELT, Tableau</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8226979af491d173</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Plymouth, MN, USA USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90bc7581ab37aef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Associate AWS DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trinzic</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, USA USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=075accddbedd75ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Trinzic</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, USA USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26a9db3524607bc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>All IT Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Arlington, VA, USA USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38b0f69a92c9c2f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Enterprise Imaging Solutions Engineer – Healthcare IT-Remote within the US</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Siemens Healthineers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Malvern, PA, USA USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D45" t="n">
         <v>10.4</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>AWS, Azure, Google Cloud Platform, Hive, Scala, SQL Server, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=97b19b6f1b88b438</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AWM Technology</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, USA USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Scala, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa825f735fd4ddf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sr AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, USA USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, MySQL, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37fd53bc295db27f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AWS DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Trinzic</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, USA USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, GitHub Actions, Terraform, AWS CloudFormation, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fe15f3fd01de120</t>
         </is>
       </c>
     </row>
